--- a/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/01_raw_results/outputs_ESR_2026_run_2019.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/01_raw_results/outputs_ESR_2026_run_2019.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>645402.121334222</v>
+        <v>517923.1571476575</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>419312</v>
+        <v>309864.0358134354</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10220</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13263.09647018612</v>
+        <v>5452.096470186117</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1061914.824380057</v>
+        <v>816050.2195434923</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>94759.02203752627</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>141772.4927916464</v>
+        <v>72880.85214164623</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49494</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37821.38083555549</v>
+        <v>132064.8002240817</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>89512.83149999997</v>
+        <v>79292.83149999997</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>18709.34182489541</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>111248.1808226194</v>
+        <v>123041.5</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>68891.64065000016</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>102233.5792021696</v>
+        <v>114026.8983795503</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>306622.5656034643</v>
+        <v>202685.7237785689</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>175050.1154273807</v>
+        <v>152659.350423</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>198872.1802126308</v>
+        <v>208050</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>74716.27080905481</v>
+        <v>60000</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>182135</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="54">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7811</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>177604.3973509999</v>
+        <v>178120</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>142390.7650043807</v>
+        <v>120000</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>421210</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="79">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>85227.5</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>167406.5707137843</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>149441.7487485908</v>
+        <v>80550.10809859063</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>354643.730910441</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>438255.5</v>
       </c>
     </row>
     <row r="93">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>94243.41938852618</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>108514.5</v>
+        <v>73260</v>
       </c>
     </row>
     <row r="102">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>510182.5154025554</v>
+        <v>392923.5512159909</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>288731.64065</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>226494.4933026192</v>
+        <v>122557.6514777237</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>124896.1241226304</v>
+        <v>113102.8049452497</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>154366</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3755.728888888909</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>108779.1260738764</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>141401.3953622706</v>
+        <v>573792.2721949819</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>293099.9999999998</v>
+        <v>73260</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>293100</v>
+        <v>73260</v>
       </c>
     </row>
     <row r="146">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3755.728888888909</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>124896.1241226304</v>
+        <v>113102.8049452497</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>13418.101</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>184824.6329192288</v>
+        <v>606521.0782649225</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>13418.101</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>421696.4453456937</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>44225.58663137958</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>182268.9066712396</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>52698.03393164728</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>57643.68763137958</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>78976.15878026752</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0</v>
+        <v>154366</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>122557.6514777237</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>697631.2432198471</v>
+        <v>455299.6498724489</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>59939.16491216038</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>0</v>
+        <v>59834.77695751414</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>10694.43148701754</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>141401.3953622706</v>
+        <v>563097.8407079644</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>81280.15741143678</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>7241.130980513095</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>108779.1260738764</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>92277.01728083877</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>849523.4825</v>
+        <v>838926.0366730001</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>187237.1601966567</v>
+        <v>0</v>
       </c>
       <c r="D312" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>156784.2708090548</v>
+        <v>142068</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -8969,7 +8969,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>571838.6750420572</v>
+        <v>1004229.551874768</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1713572.579193929</v>
+        <v>1493732.579193929</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -17993,10 +17993,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>645402.121334222</v>
+        <v>517923.1571476575</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7763544915510945</v>
+        <v>0.6230099902657177</v>
       </c>
     </row>
     <row r="9">
@@ -18047,10 +18047,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>419312</v>
+        <v>309864.0358134354</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.7389820367970281</v>
       </c>
     </row>
     <row r="12">
@@ -18101,10 +18101,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10220</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -18137,10 +18137,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13263.09647018612</v>
+        <v>5452.096470186117</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3229977831399968</v>
+        <v>0.1327755609177745</v>
       </c>
     </row>
     <row r="17">
@@ -18209,10 +18209,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1061914.824380057</v>
+        <v>816050.2195434923</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5328969625695034</v>
+        <v>0.4095155970280194</v>
       </c>
     </row>
     <row r="21">
@@ -18227,10 +18227,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>94759.02203752627</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.3054279517728486</v>
       </c>
     </row>
     <row r="22">
@@ -18245,10 +18245,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>141772.4927916464</v>
+        <v>72880.85214164623</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5317149739497112</v>
+        <v>0.2733382169902253</v>
       </c>
     </row>
     <row r="23">
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49494</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37821.38083555549</v>
+        <v>132064.8002240817</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1075344764085464</v>
+        <v>0.3754891765015941</v>
       </c>
     </row>
     <row r="27">
@@ -18353,10 +18353,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>89512.83149999997</v>
+        <v>79292.83149999997</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5165788310371472</v>
+        <v>0.4575991790170941</v>
       </c>
     </row>
     <row r="29">
@@ -18371,10 +18371,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>18709.34182489541</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.05502197375819892</v>
       </c>
     </row>
     <row r="30">
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>111248.1808226194</v>
+        <v>123041.5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9041516953435983</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -18515,10 +18515,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>68891.64065000016</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3956901906895274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>102233.5792021696</v>
+        <v>114026.8983795503</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6325474205378576</v>
+        <v>0.7055159469598834</v>
       </c>
     </row>
     <row r="40">
@@ -18659,10 +18659,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>306622.5656034643</v>
+        <v>202685.7237785689</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4411491633860196</v>
+        <v>0.2916114060269128</v>
       </c>
     </row>
     <row r="46">
@@ -18677,10 +18677,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>175050.1154273807</v>
+        <v>152659.350423</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4155886978642023</v>
+        <v>0.3624304988556777</v>
       </c>
     </row>
     <row r="47">
@@ -18785,10 +18785,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>198872.1802126308</v>
+        <v>208050</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9558864706206721</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -18803,10 +18803,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>74716.27080905481</v>
+        <v>60000</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4102246729571736</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -18983,10 +18983,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7811</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -19235,10 +19235,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>177604.3973509999</v>
+        <v>178120</v>
       </c>
       <c r="D77" t="n">
-        <v>0.997105307382663</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -19253,10 +19253,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>142390.7650043807</v>
+        <v>120000</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3380517200550335</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>85227.5</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -19397,10 +19397,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>167406.5707137843</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.3819839584757849</v>
       </c>
     </row>
     <row r="87">
@@ -19433,10 +19433,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>149441.7487485908</v>
+        <v>80550.10809859063</v>
       </c>
       <c r="D88" t="n">
-        <v>0.367497934320327</v>
+        <v>0.1980838593190662</v>
       </c>
     </row>
     <row r="89">
@@ -19505,10 +19505,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>354643.730910441</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>0.809216840200388</v>
       </c>
     </row>
     <row r="93">
@@ -19523,10 +19523,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>94243.41938852618</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.1797017237272181</v>
       </c>
     </row>
     <row r="94">
@@ -19685,10 +19685,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>510182.5154025554</v>
+        <v>392923.5512159909</v>
       </c>
       <c r="D102" t="n">
-        <v>0.8180255844626819</v>
+        <v>0.6300128050821154</v>
       </c>
     </row>
     <row r="103">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>288731.64065</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>0.6778183557839482</v>
       </c>
     </row>
     <row r="114">
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>226494.4933026192</v>
+        <v>122557.6514777237</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7025045541472636</v>
+        <v>0.3801298082495077</v>
       </c>
     </row>
     <row r="116">
@@ -19937,10 +19937,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>124896.1241226304</v>
+        <v>113102.8049452497</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2127060905359549</v>
+        <v>0.1926213134118839</v>
       </c>
     </row>
     <row r="117">
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>154366</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3755.728888888909</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.06627834837272631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -20225,10 +20225,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>108779.1260738764</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.0001087791261826555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>141401.3953622706</v>
+        <v>573792.2721949819</v>
       </c>
       <c r="D135" t="n">
-        <v>0.000141401395503672</v>
+        <v>0.0005737922727687742</v>
       </c>
     </row>
     <row r="136">
@@ -20459,10 +20459,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>293099.9999999998</v>
+        <v>73260</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -20603,10 +20603,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3755.728888888909</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>3.755728892644638e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -20837,10 +20837,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>124896.1241226304</v>
+        <v>113102.8049452497</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0001248961242475265</v>
+        <v>0.0001131028050583525</v>
       </c>
     </row>
     <row r="167">
@@ -20927,10 +20927,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>13418.101</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>1.34181010134181e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -20945,10 +20945,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>184824.6329192288</v>
+        <v>606521.0782649225</v>
       </c>
       <c r="D172" t="n">
-        <v>0.0001848246331040534</v>
+        <v>0.0006065210788714436</v>
       </c>
     </row>
     <row r="173">
@@ -20963,10 +20963,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>13418.101</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1.34181010134181e-05</v>
       </c>
     </row>
     <row r="174">
@@ -21089,10 +21089,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>421696.4453456937</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.0004216964457673902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -21197,10 +21197,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>44225.58663137958</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>4.422558667560516e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -21233,10 +21233,10 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>182268.9066712396</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.0001822689068535085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -21431,10 +21431,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>52698.03393164728</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>5.269803398434532e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -21467,10 +21467,10 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>57643.68763137958</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>5.764368768902327e-05</v>
       </c>
     </row>
     <row r="202">
@@ -21485,10 +21485,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>78976.15878026752</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>7.897615885924368e-05</v>
       </c>
     </row>
     <row r="203">
@@ -21665,10 +21665,10 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0</v>
+        <v>154366</v>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>0.000154366000154366</v>
       </c>
     </row>
     <row r="213">
@@ -22079,10 +22079,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>122557.6514777237</v>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>0.0001225576516002814</v>
       </c>
     </row>
     <row r="236">
@@ -22241,10 +22241,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>697631.2432198471</v>
+        <v>455299.6498724489</v>
       </c>
       <c r="D244" t="n">
-        <v>0.0006976312439174783</v>
+        <v>0.0004552996503277485</v>
       </c>
     </row>
     <row r="245">
@@ -22259,10 +22259,10 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>59939.16491216038</v>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>5.993916497209954e-05</v>
       </c>
     </row>
     <row r="246">
@@ -22349,10 +22349,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>0</v>
+        <v>59834.77695751414</v>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>5.983477701734892e-05</v>
       </c>
     </row>
     <row r="251">
@@ -22601,10 +22601,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>10694.43148701754</v>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>1.069443149771198e-05</v>
       </c>
     </row>
     <row r="265">
@@ -22763,10 +22763,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>141401.3953622706</v>
+        <v>563097.8407079644</v>
       </c>
       <c r="D273" t="n">
-        <v>0.000141401395503672</v>
+        <v>0.0005630978412710622</v>
       </c>
     </row>
     <row r="274">
@@ -23015,10 +23015,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>81280.15741143678</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>8.128015749271694e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -23033,10 +23033,10 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>7241.130980513095</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>7.241130987754226e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -23069,10 +23069,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>108779.1260738764</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
-        <v>0.0001087791261826555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -23087,10 +23087,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>92277.01728083877</v>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>9.227701737311579e-05</v>
       </c>
     </row>
     <row r="292">
@@ -23429,10 +23429,10 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>849523.4825</v>
+        <v>838926.0366730001</v>
       </c>
       <c r="D310" t="n">
-        <v>0.0008495234833495235</v>
+        <v>0.0008389260375119261</v>
       </c>
     </row>
     <row r="311">
@@ -23465,10 +23465,10 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>187237.1601966567</v>
+        <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>0.0001872371603838939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -23753,10 +23753,10 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>156784.2708090548</v>
+        <v>142068</v>
       </c>
       <c r="D328" t="n">
-        <v>0.0001567842709658391</v>
+        <v>0.000142068000142068</v>
       </c>
     </row>
     <row r="329">
@@ -24257,10 +24257,10 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>571838.6750420572</v>
+        <v>1004229.551874768</v>
       </c>
       <c r="D356" t="n">
-        <v>0.0005718386756138959</v>
+        <v>0.001004229552878998</v>
       </c>
     </row>
     <row r="357">
@@ -24347,10 +24347,10 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1713572.579193929</v>
+        <v>1493732.579193929</v>
       </c>
       <c r="D361" t="n">
-        <v>0.001713572580907501</v>
+        <v>0.001493732580687661</v>
       </c>
     </row>
     <row r="362">

--- a/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/01_raw_results/outputs_ESR_2026_run_2019.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/02_paper_ESR/01_raw_results/outputs_ESR_2026_run_2019.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>517923.1571476575</v>
+        <v>443206.8863386028</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>309864.0358134354</v>
+        <v>235147.7650043806</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>816050.2195434923</v>
+        <v>741333.9487344376</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>94759.02203752627</v>
+        <v>169475.292846581</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>132064.8002240817</v>
+        <v>206781.0710331364</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18709.34182489541</v>
+        <v>93425.61263395014</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>123041.5</v>
+        <v>73638.94582700002</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>114026.8983795503</v>
+        <v>64624.34420655029</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>202685.7237785689</v>
+        <v>127969.4529695142</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>152659.350423</v>
+        <v>212659.350423</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60000</v>
+        <v>74716.27080905481</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>60000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="54">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="79">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>167406.5707137843</v>
+        <v>242122.841522839</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>354643.730910441</v>
+        <v>429360.0017194957</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>94243.41938852618</v>
+        <v>168959.6901975809</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>392923.5512159909</v>
+        <v>318207.2804069361</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>288731.64065</v>
+        <v>261991.64065</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>122557.6514777237</v>
+        <v>47841.38066866901</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>113102.8049452497</v>
+        <v>162505.3591182497</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>573792.2721949819</v>
+        <v>521738.5555589272</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>73260</v>
+        <v>99999.99999999994</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>73260</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="146">
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>113102.8049452497</v>
+        <v>162505.3591182497</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>606521.0782649225</v>
+        <v>565161.7931158853</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>41359.28514903714</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>78976.15878026752</v>
+        <v>29573.60460726754</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>122557.6514777237</v>
+        <v>47841.38066866901</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>455299.6498724489</v>
+        <v>507353.3665085036</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>59834.77695751414</v>
+        <v>82497.33113051415</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>10694.43148701754</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>563097.8407079644</v>
+        <v>521738.5555589272</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>838926.0366730001</v>
+        <v>849523.4825</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>142068</v>
+        <v>156784.2708090548</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -8969,7 +8969,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1004229.551874768</v>
+        <v>952175.8352387138</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1493732.579193929</v>
+        <v>1520472.579193929</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -17993,10 +17993,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>517923.1571476575</v>
+        <v>443206.8863386028</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6230099902657177</v>
+        <v>0.5331337557181108</v>
       </c>
     </row>
     <row r="9">
@@ -18047,10 +18047,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>309864.0358134354</v>
+        <v>235147.7650043806</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7389820367970281</v>
+        <v>0.5607942653784787</v>
       </c>
     </row>
     <row r="12">
@@ -18209,10 +18209,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>816050.2195434923</v>
+        <v>741333.9487344376</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4095155970280194</v>
+        <v>0.3720209949615023</v>
       </c>
     </row>
     <row r="21">
@@ -18227,10 +18227,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>94759.02203752627</v>
+        <v>169475.292846581</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3054279517728486</v>
+        <v>0.5462539656618243</v>
       </c>
     </row>
     <row r="22">
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>132064.8002240817</v>
+        <v>206781.0710331364</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3754891765015941</v>
+        <v>0.5879239127050285</v>
       </c>
     </row>
     <row r="27">
@@ -18371,10 +18371,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18709.34182489541</v>
+        <v>93425.61263395014</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05502197375819892</v>
+        <v>0.2747537382554396</v>
       </c>
     </row>
     <row r="30">
@@ -18461,10 +18461,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>123041.5</v>
+        <v>73638.94582700002</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0.5984886873697087</v>
       </c>
     </row>
     <row r="35">
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>114026.8983795503</v>
+        <v>64624.34420655029</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7055159469598834</v>
+        <v>0.3998486852442755</v>
       </c>
     </row>
     <row r="40">
@@ -18659,10 +18659,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>202685.7237785689</v>
+        <v>127969.4529695142</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2916114060269128</v>
+        <v>0.1841143589851625</v>
       </c>
     </row>
     <row r="46">
@@ -18677,10 +18677,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>152659.350423</v>
+        <v>212659.350423</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3624304988556777</v>
+        <v>0.5048772593789321</v>
       </c>
     </row>
     <row r="47">
@@ -18803,10 +18803,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60000</v>
+        <v>74716.27080905481</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0.7471627080905481</v>
       </c>
     </row>
     <row r="54">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -19397,10 +19397,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>167406.5707137843</v>
+        <v>242122.841522839</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3819839584757849</v>
+        <v>0.5524696016886019</v>
       </c>
     </row>
     <row r="87">
@@ -19505,10 +19505,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>354643.730910441</v>
+        <v>429360.0017194957</v>
       </c>
       <c r="D92" t="n">
-        <v>0.809216840200388</v>
+        <v>0.979702483413205</v>
       </c>
     </row>
     <row r="93">
@@ -19523,10 +19523,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>94243.41938852618</v>
+        <v>168959.6901975809</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1797017237272181</v>
+        <v>0.322169417938358</v>
       </c>
     </row>
     <row r="94">
@@ -19685,10 +19685,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>392923.5512159909</v>
+        <v>318207.2804069361</v>
       </c>
       <c r="D102" t="n">
-        <v>0.6300128050821154</v>
+        <v>0.5102128918114245</v>
       </c>
     </row>
     <row r="103">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>288731.64065</v>
+        <v>261991.64065</v>
       </c>
       <c r="D113" t="n">
-        <v>0.6778183557839482</v>
+        <v>0.6150442767364992</v>
       </c>
     </row>
     <row r="114">
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>122557.6514777237</v>
+        <v>47841.38066866901</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3801298082495077</v>
+        <v>0.1483867766777365</v>
       </c>
     </row>
     <row r="116">
@@ -19937,10 +19937,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>113102.8049452497</v>
+        <v>162505.3591182497</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1926213134118839</v>
+        <v>0.2767570240630163</v>
       </c>
     </row>
     <row r="117">
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>573792.2721949819</v>
+        <v>521738.5555589272</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0005737922727687742</v>
+        <v>0.0005217385560806658</v>
       </c>
     </row>
     <row r="136">
@@ -20459,10 +20459,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>73260</v>
+        <v>99999.99999999994</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0.9999999999999994</v>
       </c>
     </row>
     <row r="146">
@@ -20837,10 +20837,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>113102.8049452497</v>
+        <v>162505.3591182497</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0001131028050583525</v>
+        <v>0.000162505359280755</v>
       </c>
     </row>
     <row r="167">
@@ -20945,10 +20945,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>606521.0782649225</v>
+        <v>565161.7931158853</v>
       </c>
       <c r="D172" t="n">
-        <v>0.0006065210788714436</v>
+        <v>0.0005651617936810471</v>
       </c>
     </row>
     <row r="173">
@@ -21089,10 +21089,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>41359.28514903714</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>4.135928519039643e-05</v>
       </c>
     </row>
     <row r="181">
@@ -21485,10 +21485,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>78976.15878026752</v>
+        <v>29573.60460726754</v>
       </c>
       <c r="D202" t="n">
-        <v>7.897615885924368e-05</v>
+        <v>2.957360463684114e-05</v>
       </c>
     </row>
     <row r="203">
@@ -22079,10 +22079,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>122557.6514777237</v>
+        <v>47841.38066866901</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0001225576516002814</v>
+        <v>4.784138071651039e-05</v>
       </c>
     </row>
     <row r="236">
@@ -22241,10 +22241,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>455299.6498724489</v>
+        <v>507353.3665085036</v>
       </c>
       <c r="D244" t="n">
-        <v>0.0004552996503277485</v>
+        <v>0.0005073533670158569</v>
       </c>
     </row>
     <row r="245">
@@ -22349,10 +22349,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>59834.77695751414</v>
+        <v>82497.33113051415</v>
       </c>
       <c r="D250" t="n">
-        <v>5.983477701734892e-05</v>
+        <v>8.249733121301149e-05</v>
       </c>
     </row>
     <row r="251">
@@ -22601,10 +22601,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>10694.43148701754</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.069443149771198e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -22763,10 +22763,10 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>563097.8407079644</v>
+        <v>521738.5555589272</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0005630978412710622</v>
+        <v>0.0005217385560806658</v>
       </c>
     </row>
     <row r="274">
@@ -23429,10 +23429,10 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>838926.0366730001</v>
+        <v>849523.4825</v>
       </c>
       <c r="D310" t="n">
-        <v>0.0008389260375119261</v>
+        <v>0.0008495234833495235</v>
       </c>
     </row>
     <row r="311">
@@ -23753,10 +23753,10 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>142068</v>
+        <v>156784.2708090548</v>
       </c>
       <c r="D328" t="n">
-        <v>0.000142068000142068</v>
+        <v>0.0001567842709658391</v>
       </c>
     </row>
     <row r="329">
@@ -24257,10 +24257,10 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1004229.551874768</v>
+        <v>952175.8352387138</v>
       </c>
       <c r="D356" t="n">
-        <v>0.001004229552878998</v>
+        <v>0.0009521758361908896</v>
       </c>
     </row>
     <row r="357">
@@ -24347,10 +24347,10 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1493732.579193929</v>
+        <v>1520472.579193929</v>
       </c>
       <c r="D361" t="n">
-        <v>0.001493732580687661</v>
+        <v>0.001520472580714401</v>
       </c>
     </row>
     <row r="362">
